--- a/hanyang-apply-bot/Hanyang_Students_Template.xlsx
+++ b/hanyang-apply-bot/Hanyang_Students_Template.xlsx
@@ -890,7 +890,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Marked (confirm)</t>
+          <t>Marked</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Participate | Don't participate (direct placement into Level 1) (confirm)</t>
+          <t>Participate | Don't participate (direct placement into Level 1)</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Lump-sum payment (confirm) | Installment (confirm)</t>
+          <t>Lump-sum payment | Installment</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Enter a university (confirm) | Employment (confirm) | Interest / Culture (confirm) | Others (confirm)</t>
+          <t>Enter a university | Employment | Interest / Culture | Others</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1 semester (confirm) | 2 semesters (confirm) | 3 semesters (confirm) | 4 semesters (confirm)</t>
+          <t>1 semester | 2 semesters | 3 semesters | 4 semesters</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Lump-sum payment (confirm)</t>
+          <t>Lump-sum payment</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Enter a university (confirm)</t>
+          <t>Enter a university</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>1 semester (confirm)</t>
+          <t>1 semester</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Don't participate (direct placement into Level 1) (confirm)</t>
+          <t>Don't participate (direct placement into Level 1)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Installment (confirm)</t>
+          <t>Installment</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Employment (confirm)</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>2 semesters (confirm)</t>
+          <t>2 semesters</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Interest / Culture (confirm)</t>
+          <t>Interest / Culture</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>3 semesters (confirm)</t>
+          <t>3 semesters</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Others (confirm)</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>4 semesters (confirm)</t>
+          <t>4 semesters</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>Don't participate (direct placement into Level 1) (confirm)</t>
+          <t>Don't participate (direct placement into Level 1)</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
-          <t>Lump-sum payment (confirm)</t>
+          <t>Lump-sum payment</t>
         </is>
       </c>
       <c r="J3" s="19" t="inlineStr">
@@ -2050,7 +2050,7 @@
       <c r="AL3" s="19" t="inlineStr"/>
       <c r="AM3" s="19" t="inlineStr">
         <is>
-          <t>Enter a university (confirm)</t>
+          <t>Enter a university</t>
         </is>
       </c>
       <c r="AN3" s="19" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AO3" s="19" t="inlineStr">
         <is>
-          <t>2 semesters (confirm)</t>
+          <t>2 semesters</t>
         </is>
       </c>
       <c r="AP3" s="19" t="inlineStr">

--- a/hanyang-apply-bot/Hanyang_Students_Template.xlsx
+++ b/hanyang-apply-bot/Hanyang_Students_Template.xlsx
@@ -341,16 +341,6 @@
         <t>1–8.</t>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
-      <text>
-        <t>CONFIRM exact wording.</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>CONFIRM options.</t>
-      </text>
-    </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
         <t>Folder under uploads/ with photo.jpg, passport.jpg, education.pdf, gap.pdf, financial.pdf, family.pdf, other.pdf. Keep format e.g. NN_FAMILY_GIVEN.</t>
@@ -418,7 +408,7 @@
     </comment>
     <comment ref="AE2" authorId="0" shapeId="0">
       <text>
-        <t>Only if they already hold a visa. CONFIRM.</t>
+        <t>Only if they already hold a visa.</t>
       </text>
     </comment>
     <comment ref="AG2" authorId="0" shapeId="0">
@@ -434,16 +424,6 @@
     <comment ref="AJ2" authorId="0" shapeId="0">
       <text>
         <t>e.g. 2022-01 ~ 2022-06.</t>
-      </text>
-    </comment>
-    <comment ref="AM2" authorId="0" shapeId="0">
-      <text>
-        <t>CONFIRM options.</t>
-      </text>
-    </comment>
-    <comment ref="AO2" authorId="0" shapeId="0">
-      <text>
-        <t>CONFIRM options.</t>
       </text>
     </comment>
     <comment ref="AS2" authorId="0" shapeId="0">
@@ -754,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -950,7 +930,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Participate | Don't participate (direct placement into Level 1)</t>
+          <t>Y : I will participate in the offline level test | N : I agree to start directly with Level 1 classes without taking the level test</t>
         </is>
       </c>
     </row>
@@ -969,120 +949,144 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>PreKorean</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Lump-sum payment | Installment</t>
+          <t>Yes (will automatically be assigned to level 1 without level test) | No</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Male | Female</t>
+          <t>Account Number | Flywire</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Undergraduate | Postgraduate or Higher | High School</t>
+          <t>Male | Female</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Enter a university | Employment | Interest / Culture | Others</t>
+          <t>Undergraduate | Postgraduate or Higher | High School</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>AimLevel</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Level 1 | Level 2 | Level 3 | Level 4 | Level 5 | Level 6</t>
+          <t>To Enter University | Hobby | TOPIK test | Find Job in Korea | Find Job in other Country | Other</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>EstPeriod</t>
+          <t>AimLevel</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1 semester | 2 semesters | 3 semesters | 4 semesters</t>
+          <t>Level 1 | Level 2 | Level 3 | Level 4 | Level 5 | Level 6</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>PrefLanguage</t>
+          <t>EstPeriod</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Korean | English | Chinese | Japanese | Others</t>
+          <t>3 months | 6 months | 9 months | 1 year | 1~2 years | 2 years</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Messenger</t>
+          <t>PrefLanguage</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Kakao | Wechat | Line</t>
+          <t>English | Chinese | Japanese | Korean</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>YesBlank</t>
+          <t>Messenger</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Kakao | Wechat | Line</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>YesBlank</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>VisaStatus</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>B-1 | B-2 | C-2 | C-3 | C-6 | D-1 | D-2 | D-4 | D-6 | D-8 | E-1 | E-2 | E-3 | E-6 | E-7 | E-9 | F-1 | F-2 | F-3 | F-4 | F-5 | F-6 | H-1 | H-2 | No Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>Nationality</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Bangladesh | India | Pakistan | Nepal | Sri Lanka | Bhutan | Vietnam | China | Indonesia | Uzbekistan | Mongolia | Myanmar | Philippines | Thailand | Japan | Others</t>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Bangladesh | India | Pakistan | Nepal | Srilanka | Bhutan | Vietnam | China | Indonesia | Uzbekistan | Mongolia | Myanmar | Philippines | Thailand | Japan</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1122,6 +1126,8 @@
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,50 +1153,60 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
+          <t>PreKorean</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>AimLevel</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>EstPeriod</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>PrefLanguage</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Messenger</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>YesBlank</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>VisaStatus</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Nationality</t>
         </is>
@@ -1209,7 +1225,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Participate</t>
+          <t>Y : I will participate in the offline level test</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1219,50 +1235,60 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Lump-sum payment</t>
+          <t>Yes (will automatically be assigned to level 1 without level test)</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
+          <t>Account Number</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Enter a university</t>
-        </is>
-      </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
+          <t>To Enter University</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>1 semester</t>
-        </is>
-      </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
           <t>Kakao</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>B-1</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>Bangladesh</t>
         </is>
@@ -1281,7 +1307,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Don't participate (direct placement into Level 1)</t>
+          <t>N : I agree to start directly with Level 1 classes without taking the level test</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1291,45 +1317,55 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Installment</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
+          <t>Flywire</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Postgraduate or Higher</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
+          <t>Hobby</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>2 semesters</t>
-        </is>
-      </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
           <t>Wechat</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>B-2</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
@@ -1346,37 +1382,42 @@
           <t>Don't Mind (Automatically assigned to the afternoon half.)</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>High School</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Interest / Culture</t>
-        </is>
-      </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
+          <t>TOPIK test</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>3 semesters</t>
-        </is>
-      </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>9 months</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
@@ -1388,27 +1429,32 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
+          <t>Find Job in Korea</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
           <t>Level 4</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>4 semesters</t>
-        </is>
-      </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Japanese</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>Nepal</t>
         </is>
@@ -1422,17 +1468,27 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
+          <t>Find Job in other Country</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
           <t>Level 5</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
+          <t>1~2 years</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>C-6</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>Srilanka</t>
         </is>
       </c>
     </row>
@@ -1444,10 +1500,25 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
           <t>Level 6</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>Bhutan</t>
         </is>
@@ -1459,7 +1530,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
@@ -1471,65 +1547,168 @@
           <t>8</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="N10" s="6" t="inlineStr">
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="N11" s="6" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="N12" s="6" t="inlineStr">
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>Mongolia</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="N13" s="6" t="inlineStr">
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>E-2</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>Myanmar</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="N14" s="6" t="inlineStr">
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>E-3</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="N15" s="6" t="inlineStr">
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>E-6</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="N16" s="6" t="inlineStr">
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>E-7</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>Others</t>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>E-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>F-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>F-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>F-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>F-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>F-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>F-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>H-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>H-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>No Visa</t>
         </is>
       </c>
     </row>
@@ -1552,10 +1731,10 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -1925,7 +2104,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>Don't participate (direct placement into Level 1)</t>
+          <t>N : I agree to start directly with Level 1 classes without taking the level test</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -1940,7 +2119,7 @@
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
-          <t>Lump-sum payment</t>
+          <t>Account Number</t>
         </is>
       </c>
       <c r="J3" s="19" t="inlineStr">
@@ -2050,7 +2229,7 @@
       <c r="AL3" s="19" t="inlineStr"/>
       <c r="AM3" s="19" t="inlineStr">
         <is>
-          <t>Enter a university</t>
+          <t>To Enter University</t>
         </is>
       </c>
       <c r="AN3" s="19" t="inlineStr">
@@ -2060,7 +2239,7 @@
       </c>
       <c r="AO3" s="19" t="inlineStr">
         <is>
-          <t>2 semesters</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="AP3" s="19" t="inlineStr">
@@ -5942,7 +6121,7 @@
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="D1:I1"/>
   </mergeCells>
-  <dataValidations count="16">
+  <dataValidations count="17">
     <dataValidation sqref="D3:D78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
       <formula1>Lists!$A$2:$A$9</formula1>
     </dataValidation>
@@ -5953,43 +6132,46 @@
       <formula1>Lists!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$D$2:$D$3</formula1>
+      <formula1>Lists!$E$2:$E$3</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
       <formula1>Lists!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$E$2:$E$3</formula1>
+      <formula1>Lists!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation sqref="N3:N78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$F$2:$F$3</formula1>
+      <formula1>Lists!$G$2:$G$3</formula1>
     </dataValidation>
     <dataValidation sqref="R3:R78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$M$2:$M$2</formula1>
+      <formula1>Lists!$N$2:$N$2</formula1>
     </dataValidation>
     <dataValidation sqref="V3:V78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$L$2:$L$4</formula1>
+      <formula1>Lists!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z3:Z78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$K$2:$K$6</formula1>
+      <formula1>Lists!$L$2:$L$5</formula1>
     </dataValidation>
     <dataValidation sqref="AC3:AC78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$G$2:$G$4</formula1>
+      <formula1>Lists!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD3:AD78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
       <formula1>Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE3:AE78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
+      <formula1>Lists!$O$2:$O$26</formula1>
     </dataValidation>
     <dataValidation sqref="AH3:AH78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
       <formula1>Lists!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation sqref="AM3:AM78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$H$2:$H$5</formula1>
+      <formula1>Lists!$I$2:$I$7</formula1>
     </dataValidation>
     <dataValidation sqref="AN3:AN78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$I$2:$I$7</formula1>
+      <formula1>Lists!$J$2:$J$7</formula1>
     </dataValidation>
     <dataValidation sqref="AO3:AO78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the dropdown (see the Lists tab)." type="list">
-      <formula1>Lists!$J$2:$J$5</formula1>
+      <formula1>Lists!$K$2:$K$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hanyang-apply-bot/Hanyang_Students_Template.xlsx
+++ b/hanyang-apply-bot/Hanyang_Students_Template.xlsx
@@ -235,10 +235,10 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
